--- a/results/mmnl_summary_statistics.xlsx
+++ b/results/mmnl_summary_statistics.xlsx
@@ -6084,7 +6084,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>6.734060316326328</v>
+        <v>6.734060316326327</v>
       </c>
       <c r="C3" t="n">
         <v>7.847941726131973</v>
@@ -6209,7 +6209,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>7.044965441843605</v>
+        <v>7.044965441843604</v>
       </c>
       <c r="D3" t="n">
         <v>7.268131606569785</v>
@@ -6302,7 +6302,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>3.663171809323853</v>
+        <v>3.663171809323852</v>
       </c>
       <c r="D6" t="n">
         <v>3.608872795459947</v>
@@ -6367,7 +6367,7 @@
         <v>7.188601043835869</v>
       </c>
       <c r="D8" t="n">
-        <v>7.788808757105863</v>
+        <v>7.788808757105862</v>
       </c>
       <c r="E8" t="n">
         <v>-1.290987760738764e-07</v>
@@ -6727,7 +6727,7 @@
         <v>6.788687035629144</v>
       </c>
       <c r="D4" t="n">
-        <v>6.492606323080772</v>
+        <v>6.492606323080771</v>
       </c>
       <c r="E4" t="n">
         <v>3.907044187885906e-08</v>
@@ -6879,7 +6879,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>6.632858285407794</v>
+        <v>6.632858285407795</v>
       </c>
       <c r="D9" t="n">
         <v>5.270869135954228</v>
@@ -6910,7 +6910,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>7.000961488712757</v>
+        <v>7.000961488712756</v>
       </c>
       <c r="D10" t="n">
         <v>6.701846260605739</v>

--- a/results/mmnl_summary_statistics.xlsx
+++ b/results/mmnl_summary_statistics.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Mean" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Std" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Details" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Mean" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Std" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Details" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="All Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RS2_Mean" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RS2_Std" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RS2_Details" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RS4_Mean" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RS4_Std" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RS4_Details" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Comparison" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6367,7 +6367,7 @@
         <v>7.188601043835869</v>
       </c>
       <c r="D8" t="n">
-        <v>7.788808757105862</v>
+        <v>7.788808757105863</v>
       </c>
       <c r="E8" t="n">
         <v>-1.290987760738764e-07</v>

--- a/results/mmnl_summary_statistics.xlsx
+++ b/results/mmnl_summary_statistics.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RS2_Mean" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RS2_Std" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RS2_Details" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RS4_Mean" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RS4_Std" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RS4_Details" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Comparison" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Mean" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Std" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS2_Details" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Mean" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Std" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RS4_Details" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6367,7 +6367,7 @@
         <v>7.188601043835869</v>
       </c>
       <c r="D8" t="n">
-        <v>7.788808757105863</v>
+        <v>7.788808757105862</v>
       </c>
       <c r="E8" t="n">
         <v>-1.290987760738764e-07</v>
